--- a/СОТИПБ-болванка.xlsx
+++ b/СОТИПБ-болванка.xlsx
@@ -148,7 +148,12 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Вводите данные начиная со строки 2. Например: 5-65/2; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+        <t>Вводите данные начиная со строки 2. Архивный номер, если C пуст. Например: 5-65/2; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Вводите данные начиная со строки 2. Новый архивный номер: при наличии он имеет приоритет над B; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -158,12 +163,12 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Вводите данные начиная со строки 2. Например: 159ст или 600/630; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+        <t>Вводите данные начиная со строки 2. Дословно переносится в D свода. Например: 159ст или 600/630; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Вводите данные начиная со строки 2. Например: 3.3/0.2; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+        <t>Вводите данные начиная со строки 2. Дословно переносится в C свода. Например: 3.3/0.2; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -178,17 +183,17 @@
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Необязательное уточнение для свода. Если исходный «лист 1» уже содержит правильное значение, оставьте пустым.</t>
+        <t>Необязательное уточнение. Q/R используются только если соответственно F/E в этой строке пусты; P уточняет тип ПОО.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Необязательное уточнение для свода. Если исходный «лист 1» уже содержит правильное значение, оставьте пустым.</t>
+        <t>Необязательное уточнение. Q/R используются только если соответственно F/E в этой строке пусты; P уточняет тип ПОО.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>Необязательное уточнение для свода. Если исходный «лист 1» уже содержит правильное значение, оставьте пустым.</t>
+        <t>Необязательное уточнение. Q/R используются только если соответственно F/E в этой строке пусты; P уточняет тип ПОО.</t>
       </text>
     </comment>
   </commentList>

--- a/СОТИПБ-болванка.xlsx
+++ b/СОТИПБ-болванка.xlsx
@@ -163,12 +163,12 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Вводите данные начиная со строки 2. Дословно переносится в D свода. Например: 159ст или 600/630; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+        <t>Вводите данные начиная со строки 2. Число + вид прокладки H в D свода; для 600/630 — две строки с было/стало; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Вводите данные начиная со строки 2. Дословно переносится в C свода. Например: 3.3/0.2; пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
+        <t>Вводите данные начиная со строки 2. Для 3.3/0.2 в C свода — две строки: 3.3 (было), 0.2 (стало); пустые ячейки допускаются, но в своде не будут заполняться догадками.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
